--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486899_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486899_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2565</v>
+        <v>3.2299</v>
       </c>
       <c r="E2" t="n">
-        <v>3.316</v>
+        <v>4.1412</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.0595</v>
+        <v>-0.9113</v>
       </c>
       <c r="G2" t="n">
         <v>3.9593</v>
@@ -610,13 +610,13 @@
         <v>0.8214</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.2573</v>
+        <v>-0.2838</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.3679</v>
+        <v>-0.5426</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1106</v>
+        <v>0.2588</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2402</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1378</v>
+        <v>1.7391</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7279</v>
+        <v>1.5071</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4099</v>
+        <v>0.232</v>
       </c>
       <c r="G3" t="n">
         <v>0.2828</v>
@@ -688,13 +688,13 @@
         <v>1.0267</v>
       </c>
       <c r="S3" t="n">
-        <v>1.0049</v>
+        <v>0.6063</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1663</v>
+        <v>-0.0545</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8386</v>
+        <v>0.6607</v>
       </c>
       <c r="V3" t="n">
         <v>1.8768</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. KANE</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,40 +721,40 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4865</v>
+        <v>0.1214</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4298</v>
+        <v>0.2801</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9163</v>
+        <v>-0.1587</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.0395</v>
+        <v>-0.5898</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8107</v>
+        <v>0.1493</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2288</v>
+        <v>-0.7391</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.4164</v>
+        <v>0.8226</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.5348000000000001</v>
+        <v>0.7042</v>
       </c>
       <c r="L4" t="n">
         <v>0.1184</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6231</v>
+        <v>-1.4124</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2759</v>
+        <v>-0.5548999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3472</v>
+        <v>-0.8575</v>
       </c>
       <c r="P4" t="n">
         <v>1.4374</v>
@@ -766,19 +766,19 @@
         <v>1.4374</v>
       </c>
       <c r="S4" t="n">
-        <v>2.843</v>
+        <v>-0.3681</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3829</v>
+        <v>-0.5425</v>
       </c>
       <c r="U4" t="n">
-        <v>1.4601</v>
+        <v>0.1744</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7544</v>
+        <v>-0.3581</v>
       </c>
       <c r="W4" t="n">
-        <v>-1.3963</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>-0.3581</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>S. KANE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,40 +799,40 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4954</v>
+        <v>-0.1458</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.09959999999999999</v>
+        <v>-1.41</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3958</v>
+        <v>1.2642</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5898</v>
+        <v>-1.0395</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1493</v>
+        <v>-0.8107</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7391</v>
+        <v>-0.2288</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8226</v>
+        <v>-0.4164</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7042</v>
+        <v>-0.5348000000000001</v>
       </c>
       <c r="L5" t="n">
         <v>0.1184</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4124</v>
+        <v>-0.6231</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5548999999999999</v>
+        <v>-0.2759</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8575</v>
+        <v>-0.3472</v>
       </c>
       <c r="P5" t="n">
         <v>1.4374</v>
@@ -844,19 +844,19 @@
         <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.9849</v>
+        <v>1.2107</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9222</v>
+        <v>0.4028</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.06270000000000001</v>
+        <v>0.8079</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3581</v>
+        <v>-1.7544</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-1.3963</v>
       </c>
       <c r="X5" t="n">
         <v>-0.3581</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. MIKHAILOV PALTARAK</t>
+          <t>X. TORRENT BAYÉ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6889</v>
+        <v>-0.9928</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.282</v>
+        <v>-0.9712</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4069</v>
+        <v>-0.0217</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.4998</v>
+        <v>-1.7458</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.9265</v>
+        <v>-0.5485</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.5733</v>
+        <v>-1.1974</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.5569</v>
+        <v>-0.5448</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6011</v>
+        <v>1.5607</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.1579</v>
+        <v>-2.1055</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.9429</v>
+        <v>-1.2011</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.5275</v>
+        <v>-2.1091</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4154</v>
+        <v>0.9081</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.0534</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0267</v>
+        <v>2.0534</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8108</v>
+        <v>-0.2442</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6506</v>
+        <v>-0.6666</v>
       </c>
       <c r="U6" t="n">
-        <v>1.1602</v>
+        <v>0.4225</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.0563</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3491</v>
+        <v>0.2402</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3491</v>
+        <v>-1.2965</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>F. ADEBAYO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.1738</v>
+        <v>-2.1284</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7964</v>
+        <v>-1.5987</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3774</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.7458</v>
+        <v>-1.0786</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5485</v>
+        <v>-2.0339</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.1974</v>
+        <v>0.9552</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.5448</v>
+        <v>0.4595</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5607</v>
+        <v>-0.1455</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.1055</v>
+        <v>0.605</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2011</v>
+        <v>-1.5382</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.1091</v>
+        <v>-1.8884</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9081</v>
+        <v>0.3502</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0534</v>
+        <v>0.8214</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.4251</v>
+        <v>0.4726</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.4919</v>
+        <v>-0.5736</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0668</v>
+        <v>1.0462</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0563</v>
+        <v>-2.3437</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2402</v>
+        <v>-0.4579</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.2965</v>
+        <v>-1.8858</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. ADEBAYO</t>
+          <t>J. GOLSON</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.8491</v>
+        <v>-2.8365</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.3194</v>
+        <v>-1.5337</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-1.3029</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0786</v>
+        <v>-2.3337</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.0339</v>
+        <v>-0.3179</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9552</v>
+        <v>-2.0158</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4595</v>
+        <v>0.06270000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.1455</v>
+        <v>0.4317</v>
       </c>
       <c r="L8" t="n">
-        <v>0.605</v>
+        <v>-0.369</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5382</v>
+        <v>-2.3964</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8884</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.3502</v>
+        <v>-1.6468</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8214</v>
+        <v>0.4107</v>
       </c>
       <c r="Q8" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.248</v>
+        <v>-0.2064</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.2943</v>
+        <v>-0.5697</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0462</v>
+        <v>0.3633</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.3437</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.4579</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8858</v>
+        <v>-0.7072000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. GOLSON</t>
+          <t>M. MIKHAILOV PALTARAK</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5876</v>
+        <v>-3.1162</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.018</v>
+        <v>-2.2351</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5696</v>
+        <v>-0.8812</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.3337</v>
+        <v>-3.4998</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3179</v>
+        <v>-1.9265</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0158</v>
+        <v>-1.5733</v>
       </c>
       <c r="J9" t="n">
-        <v>0.06270000000000001</v>
+        <v>-0.5569</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4317</v>
+        <v>0.6011</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.369</v>
+        <v>-1.1579</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3964</v>
+        <v>-2.9429</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-2.5275</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6468</v>
+        <v>-0.4154</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4107</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>-1.0267</v>
       </c>
       <c r="R9" t="n">
-        <v>1.4374</v>
+        <v>1.0267</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9574</v>
+        <v>0.3835</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.054</v>
+        <v>-0.3024</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0965</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7072000000000001</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3491</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.7072000000000001</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-9.0136</v>
+        <v>-8.4808</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3997</v>
+        <v>-4.1633</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.6139</v>
+        <v>-4.3175</v>
       </c>
       <c r="G10" t="n">
         <v>-6.6376</v>
@@ -1234,13 +1234,13 @@
         <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9222</v>
+        <v>-0.3894</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5465</v>
+        <v>-0.3101</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3757</v>
+        <v>-0.0793</v>
       </c>
       <c r="V10" t="n">
         <v>-1.6591</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.9276</v>
+        <v>-12.6101</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.301</v>
+        <v>-5.983599999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-6.6266</v>
+        <v>-6.6268</v>
       </c>
       <c r="G11" t="n">
         <v>-12.6827</v>
@@ -1282,7 +1282,7 @@
         <v>-12.6829</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.000100000000000211</v>
+        <v>-0.0001000000000006551</v>
       </c>
       <c r="J11" t="n">
         <v>5.1471</v>
@@ -1312,13 +1312,13 @@
         <v>12.3206</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1362000000000004</v>
+        <v>1.1812</v>
       </c>
       <c r="T11" t="n">
-        <v>-4.477</v>
+        <v>-3.1592</v>
       </c>
       <c r="U11" t="n">
-        <v>4.3406</v>
+        <v>4.3405</v>
       </c>
       <c r="V11" t="n">
         <v>-6.2422</v>
@@ -1327,7 +1327,7 @@
         <v>-0.7845</v>
       </c>
       <c r="X11" t="n">
-        <v>-5.4577</v>
+        <v>-5.457699999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>6.8909</v>
+        <v>7.3076</v>
       </c>
       <c r="E12" t="n">
-        <v>3.0964</v>
+        <v>2.8872</v>
       </c>
       <c r="F12" t="n">
-        <v>3.7945</v>
+        <v>4.4204</v>
       </c>
       <c r="G12" t="n">
         <v>5.2915</v>
@@ -1390,13 +1390,13 @@
         <v>1.2321</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.0166</v>
+        <v>0.4001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6201</v>
+        <v>-0.8293</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6035</v>
+        <v>1.2294</v>
       </c>
       <c r="V12" t="n">
         <v>0.5893</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.9375</v>
+        <v>4.117</v>
       </c>
       <c r="E13" t="n">
-        <v>1.5032</v>
+        <v>1.294</v>
       </c>
       <c r="F13" t="n">
-        <v>2.4343</v>
+        <v>2.823</v>
       </c>
       <c r="G13" t="n">
         <v>3.0273</v>
@@ -1468,13 +1468,13 @@
         <v>1.2321</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3219</v>
+        <v>-0.1423</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7518</v>
+        <v>-0.961</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4299</v>
+        <v>0.8187</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.2307</v>
+        <v>2.5209</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1394</v>
+        <v>-0.0699</v>
       </c>
       <c r="F14" t="n">
-        <v>3.0913</v>
+        <v>2.5908</v>
       </c>
       <c r="G14" t="n">
         <v>2.4641</v>
@@ -1546,13 +1546,13 @@
         <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>1.5961</v>
+        <v>0.8864</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6860000000000001</v>
+        <v>-0.8952</v>
       </c>
       <c r="U14" t="n">
-        <v>2.2821</v>
+        <v>1.7816</v>
       </c>
       <c r="V14" t="n">
         <v>-0.8295</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.281</v>
+        <v>1.0422</v>
       </c>
       <c r="E15" t="n">
-        <v>0.773</v>
+        <v>0.5637</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5081</v>
+        <v>0.4784</v>
       </c>
       <c r="G15" t="n">
         <v>0.4283</v>
@@ -1624,13 +1624,13 @@
         <v>0.2053</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7357</v>
+        <v>0.4969</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5656</v>
+        <v>0.3564</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1701</v>
+        <v>0.1405</v>
       </c>
       <c r="V15" t="n">
         <v>0.9384</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4902</v>
+        <v>0.9992</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6848</v>
+        <v>3.3125</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.1946</v>
+        <v>-2.3132</v>
       </c>
       <c r="G16" t="n">
         <v>0.6698</v>
@@ -1702,13 +1702,13 @@
         <v>0.616</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0441</v>
+        <v>0.465</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7905</v>
+        <v>-0.1628</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7464</v>
+        <v>0.6278</v>
       </c>
       <c r="V16" t="n">
         <v>0.4805</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1645</v>
+        <v>0.7607</v>
       </c>
       <c r="E17" t="n">
         <v>-2.1797</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3441</v>
+        <v>2.9404</v>
       </c>
       <c r="G17" t="n">
         <v>0.9112</v>
@@ -1780,13 +1780,13 @@
         <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9972</v>
+        <v>-0.4009</v>
       </c>
       <c r="T17" t="n">
         <v>-0.7905</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2067</v>
+        <v>0.3895</v>
       </c>
       <c r="V17" t="n">
         <v>3.5359</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. MUÑOZ SAMATAN</t>
+          <t>O. ALVARADO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1197</v>
+        <v>0.3565</v>
       </c>
       <c r="E18" t="n">
-        <v>2.2151</v>
+        <v>-3.0341</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.3348</v>
+        <v>3.3906</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1178</v>
+        <v>3.2273</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.9311</v>
+        <v>2.9062</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1866</v>
+        <v>0.3211</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4442</v>
+        <v>2.0105</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.016</v>
+        <v>2.0634</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4602</v>
+        <v>-0.0529</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5619</v>
+        <v>1.2168</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9151</v>
+        <v>0.8428</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.6468</v>
+        <v>0.374</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-2.8748</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2053</v>
+        <v>-4.1068</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="S18" t="n">
-        <v>0.7578</v>
+        <v>0.004</v>
       </c>
       <c r="T18" t="n">
-        <v>0.736</v>
+        <v>-0.9378</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0218</v>
+        <v>0.9417</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. ALVARADO RODRIGUEZ</t>
+          <t>G. COLOM BARRUFET</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4943</v>
+        <v>0.1574</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.3479</v>
+        <v>2.2621</v>
       </c>
       <c r="F19" t="n">
-        <v>2.8536</v>
+        <v>-2.1047</v>
       </c>
       <c r="G19" t="n">
-        <v>3.2273</v>
+        <v>-0.5385</v>
       </c>
       <c r="H19" t="n">
-        <v>2.9062</v>
+        <v>-1.5117</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3211</v>
+        <v>0.9732</v>
       </c>
       <c r="J19" t="n">
-        <v>2.0105</v>
+        <v>1.8472</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0634</v>
+        <v>-0.4019</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0529</v>
+        <v>2.2492</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2168</v>
+        <v>-2.3857</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8428</v>
+        <v>-1.1098</v>
       </c>
       <c r="O19" t="n">
-        <v>0.374</v>
+        <v>-1.2759</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.8748</v>
+        <v>0.2053</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.1068</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2321</v>
+        <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.8468</v>
+        <v>-0.0988</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.2516</v>
+        <v>-0.1744</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4047</v>
+        <v>0.0756</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. COLOM BARRUFET</t>
+          <t>D. MUÑOZ SAMATAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5574</v>
+        <v>-0.4649</v>
       </c>
       <c r="E20" t="n">
-        <v>1.8437</v>
+        <v>1.692</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4011</v>
+        <v>-2.157</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.5385</v>
+        <v>-1.1178</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5117</v>
+        <v>-0.9311</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9732</v>
+        <v>-0.1866</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8472</v>
+        <v>1.4442</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4019</v>
+        <v>-0.016</v>
       </c>
       <c r="L20" t="n">
-        <v>2.2492</v>
+        <v>1.4602</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.3857</v>
+        <v>-2.5619</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1098</v>
+        <v>-0.9151</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2759</v>
+        <v>-1.6468</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2053</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.2053</v>
       </c>
       <c r="R20" t="n">
         <v>0.2053</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8136</v>
+        <v>0.4126</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5928</v>
+        <v>0.213</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2208</v>
+        <v>0.1996</v>
       </c>
       <c r="V20" t="n">
-        <v>0.5893</v>
+        <v>0.2402</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5893</v>
+        <v>0.2402</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8955</v>
+        <v>-0.777</v>
       </c>
       <c r="E21" t="n">
         <v>-0.1013</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7943</v>
+        <v>-0.6757</v>
       </c>
       <c r="G21" t="n">
         <v>-1.6805</v>
@@ -2092,13 +2092,13 @@
         <v>0.2053</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0868</v>
+        <v>0.2053</v>
       </c>
       <c r="T21" t="n">
         <v>-0.159</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2458</v>
+        <v>0.3643</v>
       </c>
       <c r="V21" t="n">
         <v>0.6982</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>13.9279</v>
+        <v>16.0196</v>
       </c>
       <c r="E22" t="n">
-        <v>6.6267</v>
+        <v>6.626500000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>7.3011</v>
+        <v>9.393000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>12.6827</v>
@@ -2161,7 +2161,7 @@
         <v>-3.8124</v>
       </c>
       <c r="P22" t="n">
-        <v>-5.1336</v>
+        <v>-5.133599999999999</v>
       </c>
       <c r="Q22" t="n">
         <v>-12.3204</v>
@@ -2170,13 +2170,13 @@
         <v>7.187000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1362000000000004</v>
+        <v>2.2283</v>
       </c>
       <c r="T22" t="n">
-        <v>-4.3407</v>
+        <v>-4.3406</v>
       </c>
       <c r="U22" t="n">
-        <v>4.4768</v>
+        <v>6.568700000000001</v>
       </c>
       <c r="V22" t="n">
         <v>6.242299999999999</v>
